--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K648"/>
+  <dimension ref="A1:K650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25710,6 +25710,84 @@
       <c r="K648" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>430.86</v>
+      </c>
+      <c r="C649" t="n">
+        <v>408.17</v>
+      </c>
+      <c r="D649" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="E649" t="n">
+        <v>389.14</v>
+      </c>
+      <c r="F649" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="G649" t="n">
+        <v>390.42</v>
+      </c>
+      <c r="H649" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="I649" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="J649" t="n">
+        <v>426.13</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>430.86</v>
+      </c>
+      <c r="C650" t="n">
+        <v>408.17</v>
+      </c>
+      <c r="D650" t="n">
+        <v>391.28</v>
+      </c>
+      <c r="E650" t="n">
+        <v>386.92</v>
+      </c>
+      <c r="F650" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="G650" t="n">
+        <v>390.42</v>
+      </c>
+      <c r="H650" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="I650" t="n">
+        <v>376.36</v>
+      </c>
+      <c r="J650" t="n">
+        <v>423.94</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25724,7 +25802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B656"/>
+  <dimension ref="A1:B658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32287,6 +32365,26 @@
       </c>
       <c r="B656" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -32455,28 +32553,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2368187929556107</v>
+        <v>-0.2374091398630836</v>
       </c>
       <c r="J2" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K2" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02749148752784658</v>
+        <v>0.02781088747770843</v>
       </c>
       <c r="M2" t="n">
-        <v>7.95266160023993</v>
+        <v>7.931408523078662</v>
       </c>
       <c r="N2" t="n">
-        <v>110.1144598966158</v>
+        <v>109.7773944797986</v>
       </c>
       <c r="O2" t="n">
-        <v>10.49354372443436</v>
+        <v>10.47747080548539</v>
       </c>
       <c r="P2" t="n">
-        <v>438.1708127238741</v>
+        <v>438.1771354054756</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32533,28 +32631,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1749612640550363</v>
+        <v>-0.1779304439968489</v>
       </c>
       <c r="J3" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K3" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06276079806690182</v>
+        <v>0.06502084126789698</v>
       </c>
       <c r="M3" t="n">
-        <v>3.995190558556029</v>
+        <v>3.998150938663565</v>
       </c>
       <c r="N3" t="n">
-        <v>25.37246477167887</v>
+        <v>25.36483347076824</v>
       </c>
       <c r="O3" t="n">
-        <v>5.037108771078789</v>
+        <v>5.036351206058632</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6824756214239</v>
+        <v>417.7142758721977</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32611,28 +32709,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1471956543574283</v>
+        <v>-0.1507854050017563</v>
       </c>
       <c r="J4" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K4" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07403635105878947</v>
+        <v>0.07739994618665402</v>
       </c>
       <c r="M4" t="n">
-        <v>3.068073218406416</v>
+        <v>3.076122442514872</v>
       </c>
       <c r="N4" t="n">
-        <v>15.02111113552731</v>
+        <v>15.0807774768473</v>
       </c>
       <c r="O4" t="n">
-        <v>3.875707823808099</v>
+        <v>3.883397671736349</v>
       </c>
       <c r="P4" t="n">
-        <v>402.004454797775</v>
+        <v>402.0429148519822</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32689,28 +32787,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.053818165315586</v>
+        <v>-0.0560439848971359</v>
       </c>
       <c r="J5" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K5" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00624423664473206</v>
+        <v>0.006803063124584008</v>
       </c>
       <c r="M5" t="n">
-        <v>3.952425341587674</v>
+        <v>3.953519654684014</v>
       </c>
       <c r="N5" t="n">
-        <v>25.55178438677006</v>
+        <v>25.51650488347914</v>
       </c>
       <c r="O5" t="n">
-        <v>5.054877287014004</v>
+        <v>5.051386431810492</v>
       </c>
       <c r="P5" t="n">
-        <v>393.0796545288619</v>
+        <v>393.1035018246151</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32767,28 +32865,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01198767133231006</v>
+        <v>-0.01318577261135579</v>
       </c>
       <c r="J6" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K6" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003489570202448444</v>
+        <v>0.0004248844124143947</v>
       </c>
       <c r="M6" t="n">
-        <v>3.779202139698025</v>
+        <v>3.773337167636129</v>
       </c>
       <c r="N6" t="n">
-        <v>22.81966627759364</v>
+        <v>22.76083039846905</v>
       </c>
       <c r="O6" t="n">
-        <v>4.776993434954003</v>
+        <v>4.770831206243734</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6635995802811</v>
+        <v>395.6764357378107</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32845,28 +32943,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01516858153223235</v>
+        <v>0.01313729735843815</v>
       </c>
       <c r="J7" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K7" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005398718045638295</v>
+        <v>0.0004072594784129135</v>
       </c>
       <c r="M7" t="n">
-        <v>3.836514843689791</v>
+        <v>3.83254278804617</v>
       </c>
       <c r="N7" t="n">
-        <v>23.61173595340126</v>
+        <v>23.57199033036933</v>
       </c>
       <c r="O7" t="n">
-        <v>4.859190874353596</v>
+        <v>4.855099415086094</v>
       </c>
       <c r="P7" t="n">
-        <v>393.3002185320648</v>
+        <v>393.3219812028175</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32923,28 +33021,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1010220170366144</v>
+        <v>-0.1028809334684576</v>
       </c>
       <c r="J8" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K8" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02161738971495186</v>
+        <v>0.0225306140201661</v>
       </c>
       <c r="M8" t="n">
-        <v>3.948970352501532</v>
+        <v>3.942721430819455</v>
       </c>
       <c r="N8" t="n">
-        <v>25.63939486290061</v>
+        <v>25.58796510797811</v>
       </c>
       <c r="O8" t="n">
-        <v>5.063535806420313</v>
+        <v>5.058454814266715</v>
       </c>
       <c r="P8" t="n">
-        <v>388.8392668705166</v>
+        <v>388.8591736437525</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33001,28 +33099,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1836041330926678</v>
+        <v>-0.1898662722560512</v>
       </c>
       <c r="J9" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K9" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05816096538387472</v>
+        <v>0.0617391590103652</v>
       </c>
       <c r="M9" t="n">
-        <v>4.38241281970256</v>
+        <v>4.394569629580704</v>
       </c>
       <c r="N9" t="n">
-        <v>30.26029353770048</v>
+        <v>30.48532508139327</v>
       </c>
       <c r="O9" t="n">
-        <v>5.50093569656113</v>
+        <v>5.521351744038164</v>
       </c>
       <c r="P9" t="n">
-        <v>392.6422938401072</v>
+        <v>392.7093852902144</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33079,28 +33177,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1551452250452421</v>
+        <v>0.1524692760206002</v>
       </c>
       <c r="J10" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K10" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02814814004444666</v>
+        <v>0.02736027681381026</v>
       </c>
       <c r="M10" t="n">
-        <v>5.262818707069476</v>
+        <v>5.25814039740302</v>
       </c>
       <c r="N10" t="n">
-        <v>46.12581460786308</v>
+        <v>46.04456094291391</v>
       </c>
       <c r="O10" t="n">
-        <v>6.791598825597923</v>
+        <v>6.78561426422943</v>
       </c>
       <c r="P10" t="n">
-        <v>425.1991535232312</v>
+        <v>425.22781365342</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33138,7 +33236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K648"/>
+  <dimension ref="A1:K650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70061,6 +70159,120 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.51855777217627,174.72190609209932</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.51917902077853,174.7213782963856</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.51981587599962,174.720934520435</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.52049018916552,174.72064213856936</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-36.52118216886154,174.7204617016191</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-36.52186430624322,174.72027317139006</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-36.522562504967055,174.72011423035093</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>-36.523261458444644,174.72001980804862</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>-36.52388199338576,174.72067330339246</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-36.51855777217627,174.72190609209932</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-36.51917902077853,174.7213782963856</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-36.519810890301514,174.72091399110255</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-36.520485053070786,174.72061818078762</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-36.52118216886154,174.7204617016191</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-36.52186430624322,174.72027317139006</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-36.522562504967055,174.72011423035093</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>-36.52326280764058,174.7199928371927</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>-36.52388520447856,174.72064917466207</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K650"/>
+  <dimension ref="A1:K654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25788,6 +25788,162 @@
       <c r="K650" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>428.65</v>
+      </c>
+      <c r="C651" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="D651" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="E651" t="n">
+        <v>386.92</v>
+      </c>
+      <c r="F651" t="n">
+        <v>392.88</v>
+      </c>
+      <c r="G651" t="n">
+        <v>390.59</v>
+      </c>
+      <c r="H651" t="n">
+        <v>382.27</v>
+      </c>
+      <c r="I651" t="n">
+        <v>375.87</v>
+      </c>
+      <c r="J651" t="n">
+        <v>426.03</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>428.47</v>
+      </c>
+      <c r="C652" t="n">
+        <v>408.05</v>
+      </c>
+      <c r="D652" t="n">
+        <v>391.62</v>
+      </c>
+      <c r="E652" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="F652" t="n">
+        <v>393.17</v>
+      </c>
+      <c r="G652" t="n">
+        <v>390.87</v>
+      </c>
+      <c r="H652" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="I652" t="n">
+        <v>376.42</v>
+      </c>
+      <c r="J652" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>428.07</v>
+      </c>
+      <c r="C653" t="n">
+        <v>409.02</v>
+      </c>
+      <c r="D653" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="E653" t="n">
+        <v>388.28</v>
+      </c>
+      <c r="F653" t="n">
+        <v>393.81</v>
+      </c>
+      <c r="G653" t="n">
+        <v>391.26</v>
+      </c>
+      <c r="H653" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="I653" t="n">
+        <v>377.28</v>
+      </c>
+      <c r="J653" t="n">
+        <v>424.16</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>424.34</v>
+      </c>
+      <c r="C654" t="n">
+        <v>409.46</v>
+      </c>
+      <c r="D654" t="n">
+        <v>393.17</v>
+      </c>
+      <c r="E654" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="F654" t="n">
+        <v>394.08</v>
+      </c>
+      <c r="G654" t="n">
+        <v>391.33</v>
+      </c>
+      <c r="H654" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="I654" t="n">
+        <v>376.31</v>
+      </c>
+      <c r="J654" t="n">
+        <v>425.36</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25802,7 +25958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32385,6 +32541,46 @@
       </c>
       <c r="B658" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -32553,28 +32749,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2374091398630836</v>
+        <v>-0.2427809344311647</v>
       </c>
       <c r="J2" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K2" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02781088747770843</v>
+        <v>0.02940326125076376</v>
       </c>
       <c r="M2" t="n">
-        <v>7.931408523078662</v>
+        <v>7.912326438297469</v>
       </c>
       <c r="N2" t="n">
-        <v>109.7773944797986</v>
+        <v>109.2393165454182</v>
       </c>
       <c r="O2" t="n">
-        <v>10.47747080548539</v>
+        <v>10.45176140874916</v>
       </c>
       <c r="P2" t="n">
-        <v>438.1771354054756</v>
+        <v>438.2349105278893</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32631,28 +32827,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1779304439968489</v>
+        <v>-0.1834254226736529</v>
       </c>
       <c r="J3" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K3" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06502084126789698</v>
+        <v>0.06938310481024357</v>
       </c>
       <c r="M3" t="n">
-        <v>3.998150938663565</v>
+        <v>4.001755373804945</v>
       </c>
       <c r="N3" t="n">
-        <v>25.36483347076824</v>
+        <v>25.33627427171684</v>
       </c>
       <c r="O3" t="n">
-        <v>5.036351206058632</v>
+        <v>5.033515100972365</v>
       </c>
       <c r="P3" t="n">
-        <v>417.7142758721977</v>
+        <v>417.7733431542111</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32709,28 +32905,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1507854050017563</v>
+        <v>-0.1580696740378261</v>
       </c>
       <c r="J4" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K4" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07739994618665402</v>
+        <v>0.0843612683604793</v>
       </c>
       <c r="M4" t="n">
-        <v>3.076122442514872</v>
+        <v>3.092873206825155</v>
       </c>
       <c r="N4" t="n">
-        <v>15.0807774768473</v>
+        <v>15.20696325426073</v>
       </c>
       <c r="O4" t="n">
-        <v>3.883397671736349</v>
+        <v>3.899610654188534</v>
       </c>
       <c r="P4" t="n">
-        <v>402.0429148519822</v>
+        <v>402.1212448963277</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32787,28 +32983,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0560439848971359</v>
+        <v>-0.06065467550275754</v>
       </c>
       <c r="J5" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K5" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006803063124584008</v>
+        <v>0.008041275439522266</v>
       </c>
       <c r="M5" t="n">
-        <v>3.953519654684014</v>
+        <v>3.956580146404889</v>
       </c>
       <c r="N5" t="n">
-        <v>25.51650488347914</v>
+        <v>25.44846297258704</v>
       </c>
       <c r="O5" t="n">
-        <v>5.051386431810492</v>
+        <v>5.044646962135907</v>
       </c>
       <c r="P5" t="n">
-        <v>393.1035018246151</v>
+        <v>393.153081471542</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32865,28 +33061,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01318577261135579</v>
+        <v>-0.01542594142246434</v>
       </c>
       <c r="J6" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K6" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004248844124143947</v>
+        <v>0.0005889472022795328</v>
       </c>
       <c r="M6" t="n">
-        <v>3.773337167636129</v>
+        <v>3.760950562448334</v>
       </c>
       <c r="N6" t="n">
-        <v>22.76083039846905</v>
+        <v>22.64307825354425</v>
       </c>
       <c r="O6" t="n">
-        <v>4.770831206243734</v>
+        <v>4.758474361971939</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6764357378107</v>
+        <v>395.7005227263863</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32943,28 +33139,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01313729735843815</v>
+        <v>0.009886734494294641</v>
       </c>
       <c r="J7" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K7" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004072594784129135</v>
+        <v>0.0002334756160259355</v>
       </c>
       <c r="M7" t="n">
-        <v>3.83254278804617</v>
+        <v>3.82156546798892</v>
       </c>
       <c r="N7" t="n">
-        <v>23.57199033036933</v>
+        <v>23.47075881061257</v>
       </c>
       <c r="O7" t="n">
-        <v>4.855099415086094</v>
+        <v>4.844662920225985</v>
       </c>
       <c r="P7" t="n">
-        <v>393.3219812028175</v>
+        <v>393.3569369859232</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33021,28 +33217,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1028809334684576</v>
+        <v>-0.107475343618108</v>
       </c>
       <c r="J8" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K8" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0225306140201661</v>
+        <v>0.02478873798758519</v>
       </c>
       <c r="M8" t="n">
-        <v>3.942721430819455</v>
+        <v>3.933346040559762</v>
       </c>
       <c r="N8" t="n">
-        <v>25.58796510797811</v>
+        <v>25.51659576498059</v>
       </c>
       <c r="O8" t="n">
-        <v>5.058454814266715</v>
+        <v>5.051395427501256</v>
       </c>
       <c r="P8" t="n">
-        <v>388.8591736437525</v>
+        <v>388.9085640099795</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33099,28 +33295,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1898662722560512</v>
+        <v>-0.2034420222127648</v>
       </c>
       <c r="J9" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K9" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0617391590103652</v>
+        <v>0.06956150785401571</v>
       </c>
       <c r="M9" t="n">
-        <v>4.394569629580704</v>
+        <v>4.424290102289533</v>
       </c>
       <c r="N9" t="n">
-        <v>30.48532508139327</v>
+        <v>31.0430465533952</v>
       </c>
       <c r="O9" t="n">
-        <v>5.521351744038164</v>
+        <v>5.571628716398393</v>
       </c>
       <c r="P9" t="n">
-        <v>392.7093852902144</v>
+        <v>392.8553881670232</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33177,28 +33373,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1524692760206002</v>
+        <v>0.1474591737986908</v>
       </c>
       <c r="J10" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K10" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02736027681381026</v>
+        <v>0.02592678489951594</v>
       </c>
       <c r="M10" t="n">
-        <v>5.25814039740302</v>
+        <v>5.247443936285726</v>
       </c>
       <c r="N10" t="n">
-        <v>46.04456094291391</v>
+        <v>45.86622754585</v>
       </c>
       <c r="O10" t="n">
-        <v>6.78561426422943</v>
+        <v>6.772460966727679</v>
       </c>
       <c r="P10" t="n">
-        <v>425.22781365342</v>
+        <v>425.2816804603696</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33236,7 +33432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K650"/>
+  <dimension ref="A1:K654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70273,6 +70469,234 @@
         </is>
       </c>
     </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-36.51855164303079,174.72188261333312</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-36.519176136437146,174.72136724747887</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-36.51980979967958,174.7209095003114</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-36.520485053070786,174.72061818078762</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-36.52118120460237,174.72045601949625</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-36.52186449212415,174.72027505561624</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>-36.522562065191956,174.72010475467698</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>-36.52326308082414,174.7199873761515</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>-36.523882140011104,174.72067220162398</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-36.518551143824155,174.72188070103556</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-36.519178687969955,174.72137702151173</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-36.51981177318582,174.72091762650498</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-36.52048641806942,174.72062454794553</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-36.52118174236232,174.72045918837242</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-36.52186479828088,174.72027815904758</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-36.52256200827981,174.72010352841332</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>-36.523262774189504,174.71999350589164</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>-36.523883093075625,174.7206650401289</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-36.51855003447599,174.72187645148554</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-36.51918137817214,174.7213873267427</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-36.51981377265867,174.72092585962258</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-36.52048819950779,174.72063285762653</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-36.52118292914262,174.7204661817545</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-36.521865224713345,174.72028248168417</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>-36.522562308361806,174.72010999416727</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>-36.523262294723835,174.72000309057609</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>-36.523884881903236,174.72065159855288</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-36.51853968979681,174.72183682443722</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-36.519182598469726,174.72139200128066</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-36.519815798098115,174.72093419966419</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-36.520488824167856,174.72063577141085</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-36.52118342981542,174.72046913208763</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-36.5218653012525,174.720283257542</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-36.522561987584496,174.72010308249924</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>-36.523262835516455,174.71999227994363</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>-36.523883122400676,174.72066481977518</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K654"/>
+  <dimension ref="A1:K655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25944,6 +25944,45 @@
       <c r="K654" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>421.92</v>
+      </c>
+      <c r="C655" t="n">
+        <v>410.1</v>
+      </c>
+      <c r="D655" t="n">
+        <v>394.35</v>
+      </c>
+      <c r="E655" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="F655" t="n">
+        <v>394.13</v>
+      </c>
+      <c r="G655" t="n">
+        <v>391.68</v>
+      </c>
+      <c r="H655" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="I655" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="J655" t="n">
+        <v>423.87</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25958,7 +25997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B662"/>
+  <dimension ref="A1:B663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32581,6 +32620,16 @@
       </c>
       <c r="B662" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -32749,28 +32798,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2427809344311647</v>
+        <v>-0.245768110149383</v>
       </c>
       <c r="J2" t="n">
+        <v>654</v>
+      </c>
+      <c r="K2" t="n">
         <v>653</v>
       </c>
-      <c r="K2" t="n">
-        <v>652</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02940326125076376</v>
+        <v>0.03017167853674496</v>
       </c>
       <c r="M2" t="n">
-        <v>7.912326438297469</v>
+        <v>7.916602310855529</v>
       </c>
       <c r="N2" t="n">
-        <v>109.2393165454182</v>
+        <v>109.2168765197146</v>
       </c>
       <c r="O2" t="n">
-        <v>10.45176140874916</v>
+        <v>10.45068784911858</v>
       </c>
       <c r="P2" t="n">
-        <v>438.2349105278893</v>
+        <v>438.2671640111043</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32827,28 +32876,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1834254226736529</v>
+        <v>-0.1842572577751989</v>
       </c>
       <c r="J3" t="n">
+        <v>654</v>
+      </c>
+      <c r="K3" t="n">
         <v>653</v>
       </c>
-      <c r="K3" t="n">
-        <v>652</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06938310481024357</v>
+        <v>0.07016618909749828</v>
       </c>
       <c r="M3" t="n">
-        <v>4.001755373804945</v>
+        <v>3.999841606988551</v>
       </c>
       <c r="N3" t="n">
-        <v>25.33627427171684</v>
+        <v>25.30870670828049</v>
       </c>
       <c r="O3" t="n">
-        <v>5.033515100972365</v>
+        <v>5.030775954888121</v>
       </c>
       <c r="P3" t="n">
-        <v>417.7733431542111</v>
+        <v>417.7823247415084</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32905,28 +32954,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1580696740378261</v>
+        <v>-0.159140607465204</v>
       </c>
       <c r="J4" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K4" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0843612683604793</v>
+        <v>0.08558529308462681</v>
       </c>
       <c r="M4" t="n">
-        <v>3.092873206825155</v>
+        <v>3.093394947455755</v>
       </c>
       <c r="N4" t="n">
-        <v>15.20696325426073</v>
+        <v>15.2022941220232</v>
       </c>
       <c r="O4" t="n">
-        <v>3.899610654188534</v>
+        <v>3.899011941764631</v>
       </c>
       <c r="P4" t="n">
-        <v>402.1212448963277</v>
+        <v>402.1328118007184</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32983,28 +33032,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06065467550275754</v>
+        <v>-0.06166950443716827</v>
       </c>
       <c r="J5" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K5" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008041275439522266</v>
+        <v>0.008333501136447374</v>
       </c>
       <c r="M5" t="n">
-        <v>3.956580146404889</v>
+        <v>3.956530824660158</v>
       </c>
       <c r="N5" t="n">
-        <v>25.44846297258704</v>
+        <v>25.4262379785754</v>
       </c>
       <c r="O5" t="n">
-        <v>5.044646962135907</v>
+        <v>5.042443651502256</v>
       </c>
       <c r="P5" t="n">
-        <v>393.153081471542</v>
+        <v>393.1640424042735</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33061,28 +33110,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01542594142246434</v>
+        <v>-0.0157791401624187</v>
       </c>
       <c r="J6" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K6" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005889472022795328</v>
+        <v>0.0006182888095166428</v>
       </c>
       <c r="M6" t="n">
-        <v>3.760950562448334</v>
+        <v>3.756871705268185</v>
       </c>
       <c r="N6" t="n">
-        <v>22.64307825354425</v>
+        <v>22.61047711368948</v>
       </c>
       <c r="O6" t="n">
-        <v>4.758474361971939</v>
+        <v>4.755047540634003</v>
       </c>
       <c r="P6" t="n">
-        <v>395.7005227263863</v>
+        <v>395.7043375443307</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33139,28 +33188,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009886734494294641</v>
+        <v>0.009292261990918352</v>
       </c>
       <c r="J7" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K7" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002334756160259355</v>
+        <v>0.0002069128216374283</v>
       </c>
       <c r="M7" t="n">
-        <v>3.82156546798892</v>
+        <v>3.817987979756647</v>
       </c>
       <c r="N7" t="n">
-        <v>23.47075881061257</v>
+        <v>23.44059687317474</v>
       </c>
       <c r="O7" t="n">
-        <v>4.844662920225985</v>
+        <v>4.841549015880634</v>
       </c>
       <c r="P7" t="n">
-        <v>393.3569369859232</v>
+        <v>393.3633577460132</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33217,28 +33266,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.107475343618108</v>
+        <v>-0.1085210819329422</v>
       </c>
       <c r="J8" t="n">
+        <v>654</v>
+      </c>
+      <c r="K8" t="n">
         <v>653</v>
       </c>
-      <c r="K8" t="n">
-        <v>652</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.02478873798758519</v>
+        <v>0.02532935768050915</v>
       </c>
       <c r="M8" t="n">
-        <v>3.933346040559762</v>
+        <v>3.930771275283986</v>
       </c>
       <c r="N8" t="n">
-        <v>25.51659576498059</v>
+        <v>25.49527196539634</v>
       </c>
       <c r="O8" t="n">
-        <v>5.051395427501256</v>
+        <v>5.049284302294369</v>
       </c>
       <c r="P8" t="n">
-        <v>388.9085640099795</v>
+        <v>388.9198538017853</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33295,28 +33344,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2034420222127648</v>
+        <v>-0.2067563751411169</v>
       </c>
       <c r="J9" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K9" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06956150785401571</v>
+        <v>0.07153214127163599</v>
       </c>
       <c r="M9" t="n">
-        <v>4.424290102289533</v>
+        <v>4.431595233791848</v>
       </c>
       <c r="N9" t="n">
-        <v>31.0430465533952</v>
+        <v>31.1735681692718</v>
       </c>
       <c r="O9" t="n">
-        <v>5.571628716398393</v>
+        <v>5.58332948779416</v>
       </c>
       <c r="P9" t="n">
-        <v>392.8553881670232</v>
+        <v>392.8911857268523</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33373,28 +33422,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1474591737986908</v>
+        <v>0.1458038078062544</v>
       </c>
       <c r="J10" t="n">
+        <v>654</v>
+      </c>
+      <c r="K10" t="n">
         <v>653</v>
       </c>
-      <c r="K10" t="n">
-        <v>652</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02592678489951594</v>
+        <v>0.02542421712220067</v>
       </c>
       <c r="M10" t="n">
-        <v>5.247443936285726</v>
+        <v>5.246503523900333</v>
       </c>
       <c r="N10" t="n">
-        <v>45.86622754585</v>
+        <v>45.84046986948309</v>
       </c>
       <c r="O10" t="n">
-        <v>6.772460966727679</v>
+        <v>6.770559051473009</v>
       </c>
       <c r="P10" t="n">
-        <v>425.2816804603696</v>
+        <v>425.2995539717691</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33432,7 +33481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K654"/>
+  <dimension ref="A1:K655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70697,6 +70746,63 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-36.51853297822831,174.7218111146686</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-36.519184373447715,174.72139880060888</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-36.51981886222332,174.72094681665098</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-36.52048801442331,174.72063199428302</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-36.521183522532596,174.7204696784456</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-36.52186568394814,174.72028713683127</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-36.52256223075443,174.72010832198953</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>-36.52326270728736,174.7199948432895</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>-36.523885307116146,174.7206484034241</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
